--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="494">
   <si>
     <t>Filename</t>
   </si>
@@ -808,697 +808,694 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9879,0.0008,0.0068,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.9879,0.0012,0.0000,0.0033</t>
-  </si>
-  <si>
-    <t>0.0224,0.0000,0.0000,0.9970</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0000</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9835,0.0004,0.0111,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.9808,0.0042,0.0001,0.0033</t>
+  </si>
+  <si>
+    <t>0.0225,0.0000,0.0001,0.9959</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0011,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0010,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6499,0.0080,0.2792,0.0004</t>
+  </si>
+  <si>
+    <t>0.0033,0.0005,0.9952,0.0003</t>
+  </si>
+  <si>
+    <t>0.0359,0.0004,0.9732,0.0000</t>
+  </si>
+  <si>
+    <t>0.0012,0.0009,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0001,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0382,0.9707,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9902,0.0002,0.0062,0.0001</t>
+  </si>
+  <si>
+    <t>0.8551,0.0009,0.1784,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9968,0.0018</t>
+  </si>
+  <si>
+    <t>0.0061,0.0005,0.9938,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.8059,0.1924,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.8822,0.0544,0.0242,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.0005,0.9982,0.0057</t>
+  </si>
+  <si>
+    <t>0.0102,0.9629,0.0152,0.0000</t>
+  </si>
+  <si>
+    <t>0.9971,0.0013,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0529,0.0038,0.9523,0.0018</t>
+  </si>
+  <si>
+    <t>0.0300,0.9736,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.9961,0.0028,0.0004</t>
+  </si>
+  <si>
+    <t>0.0202,0.9520,0.0313,0.0027</t>
+  </si>
+  <si>
+    <t>0.0022,0.0039,0.9903,0.0016</t>
+  </si>
+  <si>
+    <t>0.0059,0.0012,0.9903,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9993,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.9714,0.0107,0.0029</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.5478,0.0004,0.9881</t>
+  </si>
+  <si>
+    <t>0.0008,0.9990,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.2149,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0326,0.0037,0.9651,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0019,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9969,0.0010,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0037,0.9997,0.0002</t>
+  </si>
+  <si>
+    <t>0.9815,0.0158,0.0022,0.0007</t>
+  </si>
+  <si>
+    <t>0.9974,0.0014,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9677,0.9746,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9992,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9669,0.0080,0.0166,0.0001</t>
+  </si>
+  <si>
+    <t>0.9892,0.0081,0.0011,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0013,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9946,0.7408,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.7837,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.9933,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0014,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0003,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.9982,0.9585,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9817,0.9907,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5487,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9961,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.9737,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9967,0.0055,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9981,0.0020,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0009,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0040,0.0003,0.0000</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0016,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.2782,0.0022,0.7457,0.0004</t>
-  </si>
-  <si>
-    <t>0.0031,0.0004,0.9972,0.0002</t>
-  </si>
-  <si>
-    <t>0.9863,0.0003,0.0132,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9957,0.0002,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9986,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.5054,0.5999,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9938,0.0001,0.0045,0.0000</t>
-  </si>
-  <si>
-    <t>0.9629,0.0005,0.0331,0.0001</t>
-  </si>
-  <si>
-    <t>0.0028,0.0005,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0146,0.0163,0.9515,0.0030</t>
-  </si>
-  <si>
-    <t>0.0434,0.0002,0.9657,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0045</t>
-  </si>
-  <si>
-    <t>0.4407,0.5246,0.0065,0.0003</t>
-  </si>
-  <si>
-    <t>0.9687,0.0095,0.0089,0.0016</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9995,0.0035</t>
-  </si>
-  <si>
-    <t>0.0016,0.9963,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9878,0.0087,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0588,0.9506,0.0013,0.0003</t>
-  </si>
-  <si>
-    <t>0.0050,0.9879,0.0077,0.0020</t>
-  </si>
-  <si>
-    <t>0.0205,0.1952,0.5889,0.0083</t>
-  </si>
-  <si>
-    <t>0.0355,0.0015,0.9555,0.0006</t>
-  </si>
-  <si>
-    <t>0.0189,0.0031,0.9748,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0090,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0127,0.9610,0.0115,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9889,0.0014,0.3705</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.3342,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9988,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
+    <t>0.9955,0.0069,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0069,0.0099,0.9843,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9987,0.0002</t>
+  </si>
+  <si>
+    <t>0.0016,0.9991,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9976,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0028,0.9948,0.0018,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9914,0.0120,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.3806,0.0020,0.6357,0.0004</t>
+  </si>
+  <si>
+    <t>0.7510,0.0004,0.2622,0.0006</t>
+  </si>
+  <si>
+    <t>0.0328,0.0021,0.9539,0.0010</t>
+  </si>
+  <si>
+    <t>0.1639,0.0035,0.8119,0.0009</t>
+  </si>
+  <si>
+    <t>0.0004,0.2182,0.0069,0.9486</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.0529,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.9970,0.0025,0.0001</t>
+  </si>
+  <si>
+    <t>0.9249,0.0541,0.0121,0.0005</t>
+  </si>
+  <si>
+    <t>0.1632,0.7543,0.0302,0.0013</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9896,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8690,0.9972,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9600,0.0037,0.0201,0.0035</t>
+  </si>
+  <si>
+    <t>0.9054,0.0002,0.1425,0.0000</t>
+  </si>
+  <si>
+    <t>0.9901,0.0013,0.0022,0.0001</t>
+  </si>
+  <si>
+    <t>0.0085,0.0001,0.0000,0.9980</t>
+  </si>
+  <si>
+    <t>0.0000,0.0016,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9821,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0063,0.9895,0.0014,0.0033</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0429,0.9536,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0070,0.0000,0.0018,0.9958</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0658,0.0531,0.9314,0.0017</t>
+  </si>
+  <si>
+    <t>0.8509,0.0000,0.0000,0.3575</t>
+  </si>
+  <si>
+    <t>0.9553,0.0061,0.0150,0.0111</t>
+  </si>
+  <si>
+    <t>0.9792,0.0304,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9924,0.0032,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.2816,0.6430,0.0116,0.0001</t>
+  </si>
+  <si>
+    <t>0.3754,0.0053,0.6108,0.0004</t>
+  </si>
+  <si>
+    <t>0.9978,0.0003,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9976,0.0009,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0007,0.0020</t>
+  </si>
+  <si>
+    <t>0.4283,0.5856,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.3949,0.5977,0.0074,0.0001</t>
+  </si>
+  <si>
+    <t>0.9145,0.0672,0.0062,0.0003</t>
+  </si>
+  <si>
+    <t>0.0107,0.3123,0.9700,0.0025</t>
+  </si>
+  <si>
+    <t>0.9953,0.0073,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9977,0.0005,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4390,0.6852,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9870,0.0051,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9979,0.0017</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0124,0.0021,0.9880,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.0012,0.9937,0.0004</t>
+  </si>
+  <si>
+    <t>0.1277,0.0005,0.9161,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0105,0.9883,0.0003</t>
+  </si>
+  <si>
+    <t>0.0057,0.0089,0.9818,0.0005</t>
+  </si>
+  <si>
+    <t>0.0085,0.0223,0.9320,0.0007</t>
+  </si>
+  <si>
+    <t>0.9290,0.0055,0.0454,0.0002</t>
+  </si>
+  <si>
+    <t>0.9387,0.0004,0.0677,0.0003</t>
+  </si>
+  <si>
+    <t>0.7828,0.0150,0.1026,0.0039</t>
+  </si>
+  <si>
+    <t>0.0145,0.9851,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0153,0.9858,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9971,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0025,0.9973,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9610,0.0455,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9864,0.0003,0.0115,0.0000</t>
+  </si>
+  <si>
+    <t>0.9055,0.0102,0.0036,0.0274</t>
+  </si>
+  <si>
+    <t>0.9393,0.0017,0.0500,0.0005</t>
+  </si>
+  <si>
+    <t>0.9139,0.0008,0.0804,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9997,0.0030</t>
+  </si>
+  <si>
+    <t>0.0046,0.0344,0.9729,0.0040</t>
+  </si>
+  <si>
+    <t>0.0006,0.9217,0.7277,0.0008</t>
+  </si>
+  <si>
+    <t>0.0090,0.0006,0.9891,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0012,0.9984,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9957,0.0034,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0024,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0008,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0053,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9973,0.0008,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.0058,0.9982,0.0010</t>
+  </si>
+  <si>
+    <t>0.0064,0.3011,0.6722,0.0031</t>
+  </si>
+  <si>
+    <t>0.9840,0.0007,0.0069,0.0015</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.0002,0.9996,0.0003</t>
-  </si>
-  <si>
-    <t>0.9957,0.0031,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0009,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.9997,0.0029</t>
-  </si>
-  <si>
-    <t>0.9975,0.0005,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.8988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9970,0.9980,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9991,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3822,0.0057,0.6726,0.0000</t>
-  </si>
-  <si>
-    <t>0.9749,0.0107,0.0076,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.0034,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9418,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9273,0.9949,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.4933,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9848,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0284,0.9975</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.0003,0.9996</t>
-  </si>
-  <si>
-    <t>0.0004,0.0002,0.0002,0.9996</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.7629,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9869,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9084,0.8348,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.8622,0.9918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9339,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9981,0.9625,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0011,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0040,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9961,0.0025,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9955,0.0066,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9925,0.0113,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0014,0.9975,0.0001</t>
-  </si>
-  <si>
-    <t>0.9957,0.0002,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0001,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9985,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.9931,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.7734,0.2777,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.0428,0.0049,0.9468,0.0014</t>
-  </si>
-  <si>
-    <t>0.9857,0.0012,0.0103,0.0001</t>
-  </si>
-  <si>
-    <t>0.6209,0.0496,0.0489,0.0142</t>
-  </si>
-  <si>
-    <t>0.4522,0.0068,0.4023,0.0040</t>
-  </si>
-  <si>
-    <t>0.0001,0.1086,0.0004,0.9967</t>
-  </si>
-  <si>
-    <t>0.0001,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.1152,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9594,0.0336,0.0047,0.0001</t>
-  </si>
-  <si>
-    <t>0.1396,0.8504,0.0061,0.0007</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0005,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9612,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.3067,0.9975,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.0145,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6994,0.0126,0.2767,0.0011</t>
-  </si>
-  <si>
-    <t>0.6112,0.0001,0.5097,0.0000</t>
-  </si>
-  <si>
-    <t>0.9781,0.0062,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.7230,0.0001,0.0000,0.4903</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9884,0.0000</t>
-  </si>
-  <si>
-    <t>0.0113,0.9837,0.0021,0.0036</t>
-  </si>
-  <si>
-    <t>0.9973,0.0004,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.0189,0.9800,0.0013,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0239,0.0000,0.0002,0.9935</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.0085,0.0060,0.9909,0.0016</t>
-  </si>
-  <si>
-    <t>0.9945,0.0000,0.0002,0.0032</t>
-  </si>
-  <si>
-    <t>0.9980,0.0002,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.5944,0.3994,0.0055,0.0002</t>
-  </si>
-  <si>
-    <t>0.9984,0.0005,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9970,0.0013,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.2136,0.8334,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9089,0.0189,0.0367,0.0002</t>
-  </si>
-  <si>
-    <t>0.9963,0.0006,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0000,0.0008</t>
-  </si>
-  <si>
-    <t>0.9980,0.0004,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0003,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.0805,0.9195,0.0027,0.0005</t>
-  </si>
-  <si>
-    <t>0.4848,0.4127,0.0175,0.0002</t>
-  </si>
-  <si>
-    <t>0.5602,0.4276,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.0031,0.2338,0.9879,0.0009</t>
-  </si>
-  <si>
-    <t>0.9930,0.0107,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9884,0.0079,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9985,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.4283,0.6555,0.0014,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9951,0.0016,0.0011,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9990,0.0002</t>
-  </si>
-  <si>
-    <t>0.0290,0.0026,0.9748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0050,0.0411,0.9453,0.0008</t>
-  </si>
-  <si>
-    <t>0.0007,0.0004,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.4971,0.0789,0.0930,0.0115</t>
-  </si>
-  <si>
-    <t>0.1144,0.2448,0.2571,0.0003</t>
-  </si>
-  <si>
-    <t>0.0069,0.0137,0.9646,0.0004</t>
-  </si>
-  <si>
-    <t>0.4671,0.0059,0.4881,0.0006</t>
-  </si>
-  <si>
-    <t>0.9637,0.0013,0.0276,0.0003</t>
-  </si>
-  <si>
-    <t>0.2758,0.0047,0.6924,0.0019</t>
-  </si>
-  <si>
-    <t>0.0122,0.9899,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0027,0.9967,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.1784,0.8792,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.1777,0.8782,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0379,0.9674,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9787,0.0039,0.0064,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0003,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.9818,0.0011,0.0070,0.0008</t>
-  </si>
-  <si>
-    <t>0.9550,0.0022,0.0283,0.0007</t>
-  </si>
-  <si>
-    <t>0.8979,0.0323,0.0197,0.0016</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.9984,0.0026</t>
-  </si>
-  <si>
-    <t>0.0055,0.0393,0.9468,0.0046</t>
-  </si>
-  <si>
-    <t>0.0120,0.8571,0.3950,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0241,0.9964,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0022,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0007,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0044,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0006,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0164,0.9981,0.0024</t>
-  </si>
-  <si>
-    <t>0.0173,0.1217,0.7736,0.0016</t>
-  </si>
-  <si>
-    <t>0.9953,0.0002,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0007,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0057,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0310,0.0005,0.9738,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.0031,0.9946,0.0006</t>
-  </si>
-  <si>
-    <t>0.0062,0.0242,0.9800,0.0012</t>
-  </si>
-  <si>
-    <t>0.9671,0.0001,0.0397,0.0001</t>
-  </si>
-  <si>
-    <t>0.9661,0.0000,0.0456,0.0000</t>
-  </si>
-  <si>
-    <t>0.9761,0.0005,0.0184,0.0003</t>
-  </si>
-  <si>
-    <t>0.9976,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0012,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9927,0.0075,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0287,0.0056,0.9437,0.0018</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0029,0.8356,0.1379,0.0050</t>
-  </si>
-  <si>
-    <t>0.0125,0.0010,0.9819,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0007,0.9881,0.0383</t>
-  </si>
-  <si>
-    <t>0.0024,0.0007,0.9952,0.0010</t>
-  </si>
-  <si>
-    <t>0.0158,0.0015,0.9718,0.0028</t>
-  </si>
-  <si>
-    <t>0.9909,0.0000,0.0007,0.0038</t>
-  </si>
-  <si>
-    <t>0.0010,0.0053,0.0001,0.9989</t>
-  </si>
-  <si>
-    <t>0.4430,0.0002,0.0007,0.8157</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.7661,0.0207,0.0036,0.0874</t>
+    <t>0.0000,0.0008,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0248,0.9970,0.0003</t>
+  </si>
+  <si>
+    <t>0.0224,0.0006,0.9795,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9990,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0010,0.9934,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.2031,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0002,0.0046,0.0000</t>
+  </si>
+  <si>
+    <t>0.9008,0.0001,0.1266,0.0001</t>
+  </si>
+  <si>
+    <t>0.8974,0.0002,0.1203,0.0003</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9919,0.0097,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0036,0.0009,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0153,0.0025,0.9730,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0215,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0089,0.9850,0.0013</t>
+  </si>
+  <si>
+    <t>0.0018,0.0005,0.9960,0.0003</t>
+  </si>
+  <si>
+    <t>0.0342,0.0024,0.8840,0.0267</t>
+  </si>
+  <si>
+    <t>0.0127,0.0007,0.9872,0.0002</t>
+  </si>
+  <si>
+    <t>0.4785,0.0014,0.4628,0.0023</t>
+  </si>
+  <si>
+    <t>0.9874,0.0000,0.0001,0.0142</t>
+  </si>
+  <si>
+    <t>0.0007,0.0304,0.0001,0.9985</t>
+  </si>
+  <si>
+    <t>0.0373,0.0001,0.0012,0.9877</t>
+  </si>
+  <si>
+    <t>0.8996,0.0120,0.0012,0.0301</t>
   </si>
 </sst>
 </file>
@@ -1884,7 +1881,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1898,7 +1895,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1912,7 +1909,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1926,7 +1923,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1940,7 +1937,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1954,7 +1951,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1968,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1982,7 +1979,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1996,7 +1993,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2010,7 +2007,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2024,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2038,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2049,10 +2046,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2066,7 +2063,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2077,10 +2074,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2094,7 +2091,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2108,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2122,7 +2119,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2136,7 +2133,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,7 +2147,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2164,7 +2161,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2178,7 +2175,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2192,7 +2189,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,7 +2203,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2220,7 +2217,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2234,7 +2231,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2248,7 +2245,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2262,7 +2259,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2276,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2287,10 +2284,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,7 +2301,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2318,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2332,7 +2329,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2346,7 +2343,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2357,10 +2354,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2374,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2388,7 +2385,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2399,10 +2396,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2416,7 +2413,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2430,7 +2427,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2444,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2458,7 +2455,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2472,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2486,7 +2483,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2497,10 +2494,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2514,7 +2511,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2528,7 +2525,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>286</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2542,7 +2539,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2556,7 +2553,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2570,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2584,7 +2581,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2598,7 +2595,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2612,7 +2609,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2626,7 +2623,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2640,7 +2637,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2654,7 +2651,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2668,7 +2665,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2682,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2696,7 +2693,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2710,7 +2707,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>273</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2833,7 +2830,7 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>330</v>
@@ -2903,7 +2900,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
         <v>335</v>
@@ -2962,7 +2959,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2976,7 +2973,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2990,7 +2987,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3004,7 +3001,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,7 +3015,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3032,7 +3029,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3046,7 +3043,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3060,7 +3057,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3074,7 +3071,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3088,7 +3085,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3102,7 +3099,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3172,7 +3169,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3186,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3200,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3214,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3228,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3242,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3256,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3270,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3312,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3326,7 +3323,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3340,7 +3337,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3354,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3368,7 +3365,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3382,7 +3379,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3396,7 +3393,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3410,7 +3407,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3424,7 +3421,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3438,7 +3435,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3452,7 +3449,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3466,7 +3463,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,7 +3477,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3494,7 +3491,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3505,10 +3502,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3519,10 +3516,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3536,7 +3533,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3550,7 +3547,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3564,7 +3561,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3578,7 +3575,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,7 +3589,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3606,7 +3603,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,7 +3617,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3648,7 +3645,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3662,7 +3659,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3676,7 +3673,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3690,7 +3687,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3704,7 +3701,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3718,7 +3715,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3732,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3746,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3760,7 +3757,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3771,10 +3768,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3788,7 +3785,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3802,7 +3799,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3816,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3841,10 +3838,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3858,7 +3855,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3869,10 +3866,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3886,7 +3883,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3900,7 +3897,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3914,7 +3911,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>398</v>
+        <v>339</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3928,7 +3925,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3942,7 +3939,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>357</v>
+        <v>397</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3956,7 +3953,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3970,7 +3967,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3984,7 +3981,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3998,7 +3995,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4012,7 +4009,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4026,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4040,7 +4037,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4054,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4068,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4096,7 +4093,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4110,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4124,7 +4121,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4135,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D163" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4152,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4166,7 +4163,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4180,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4194,7 +4191,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4208,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4222,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4236,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4250,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>357</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4278,7 +4275,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4289,10 +4286,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,7 +4317,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4334,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4348,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4362,7 +4359,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,7 +4373,7 @@
         <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4390,7 +4387,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4404,7 +4401,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4418,7 +4415,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4432,7 +4429,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4446,7 +4443,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4460,7 +4457,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4474,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4488,7 +4485,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>358</v>
+        <v>434</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4502,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4516,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4530,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4541,10 +4538,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4555,10 +4552,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4572,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4586,7 +4583,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4600,7 +4597,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4611,10 +4608,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4628,7 +4625,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4642,7 +4639,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4656,7 +4653,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4670,7 +4667,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4684,7 +4681,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,7 +4695,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4712,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4726,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4740,7 +4737,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4754,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4768,7 +4765,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4782,7 +4779,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4793,10 +4790,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4810,7 +4807,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4824,7 +4821,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4838,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4852,7 +4849,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4866,7 +4863,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4880,7 +4877,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4894,7 +4891,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4908,7 +4905,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4922,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4936,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>465</v>
+        <v>276</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5034,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>327</v>
+        <v>429</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5062,7 +5059,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>358</v>
+        <v>473</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5076,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5090,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5104,7 +5101,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,7 +5115,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5132,7 +5129,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5146,7 +5143,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5160,7 +5157,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5174,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>461</v>
+        <v>273</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5188,7 +5185,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5202,7 +5199,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5216,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5230,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>353</v>
+        <v>276</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5244,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5258,7 +5255,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5272,7 +5269,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5283,10 +5280,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5300,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5314,7 +5311,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>486</v>
+        <v>429</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5353,7 +5350,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D250" t="s">
         <v>489</v>
@@ -5412,7 +5409,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>396</v>
+        <v>338</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5426,7 +5423,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>493</v>
+        <v>338</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5440,7 +5437,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
   </sheetData>
